--- a/project/sample-imports/patients-sample.xlsx
+++ b/project/sample-imports/patients-sample.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="111">
   <si>
     <t>file_number</t>
   </si>
@@ -103,22 +103,22 @@
     <t>Classic Saver</t>
   </si>
   <si>
-    <t>900101</t>
-  </si>
-  <si>
-    <t>Test Contact</t>
-  </si>
-  <si>
-    <t>0829990000</t>
-  </si>
-  <si>
-    <t>Sibling</t>
+    <t>900100123</t>
+  </si>
+  <si>
+    <t>Sibusiso Nkosi</t>
+  </si>
+  <si>
+    <t>0829001001</t>
+  </si>
+  <si>
+    <t>Husband</t>
   </si>
   <si>
     <t>O+</t>
   </si>
   <si>
-    <t>Penicillin</t>
+    <t>Penicillin;Latex</t>
   </si>
   <si>
     <t>Asthma</t>
@@ -127,58 +127,121 @@
     <t>Ventolin</t>
   </si>
   <si>
+    <t>Dr A Naidoo</t>
+  </si>
+  <si>
+    <t>Prefers morning appointments</t>
+  </si>
+  <si>
+    <t>MP-100002</t>
+  </si>
+  <si>
+    <t>Sipho</t>
+  </si>
+  <si>
+    <t>Dube</t>
+  </si>
+  <si>
+    <t>sipho.dube.test@example.com</t>
+  </si>
+  <si>
+    <t>7911025234080</t>
+  </si>
+  <si>
+    <t>1979-11-02</t>
+  </si>
+  <si>
+    <t>male</t>
+  </si>
+  <si>
+    <t>0821110002</t>
+  </si>
+  <si>
+    <t>Bonitas</t>
+  </si>
+  <si>
+    <t>BonComprehensive</t>
+  </si>
+  <si>
+    <t>BN4455210</t>
+  </si>
+  <si>
+    <t>Nomvula Dube</t>
+  </si>
+  <si>
+    <t>0829001002</t>
+  </si>
+  <si>
+    <t>Wife</t>
+  </si>
+  <si>
+    <t>A+</t>
+  </si>
+  <si>
+    <t>Sulfa drugs</t>
+  </si>
+  <si>
+    <t>Hypertension;Type 2 diabetes</t>
+  </si>
+  <si>
+    <t>Amlodipine;Metformin</t>
+  </si>
+  <si>
+    <t>Dr P Govender</t>
+  </si>
+  <si>
+    <t>Diabetic review every 3 months</t>
+  </si>
+  <si>
+    <t>MP-100003</t>
+  </si>
+  <si>
+    <t>Lerato</t>
+  </si>
+  <si>
+    <t>Molefe</t>
+  </si>
+  <si>
+    <t>lerato.molefe.test@example.com</t>
+  </si>
+  <si>
+    <t>9507212234087</t>
+  </si>
+  <si>
+    <t>1995-07-21</t>
+  </si>
+  <si>
+    <t>0821110003</t>
+  </si>
+  <si>
+    <t>Momentum Health</t>
+  </si>
+  <si>
+    <t>Ingwe</t>
+  </si>
+  <si>
+    <t>MM7788341</t>
+  </si>
+  <si>
+    <t>Palesa Molefe</t>
+  </si>
+  <si>
+    <t>0829001003</t>
+  </si>
+  <si>
+    <t>Mother</t>
+  </si>
+  <si>
+    <t>B-</t>
+  </si>
+  <si>
+    <t>Peanuts</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>MP-100002</t>
-  </si>
-  <si>
-    <t>Sipho</t>
-  </si>
-  <si>
-    <t>Dube</t>
-  </si>
-  <si>
-    <t>sipho.dube.test@example.com</t>
-  </si>
-  <si>
-    <t>7911025234080</t>
-  </si>
-  <si>
-    <t>1979-11-02</t>
-  </si>
-  <si>
-    <t>male</t>
-  </si>
-  <si>
-    <t>0821110002</t>
-  </si>
-  <si>
-    <t>900102</t>
-  </si>
-  <si>
-    <t>MP-100003</t>
-  </si>
-  <si>
-    <t>Lerato</t>
-  </si>
-  <si>
-    <t>Molefe</t>
-  </si>
-  <si>
-    <t>lerato.molefe.test@example.com</t>
-  </si>
-  <si>
-    <t>9507212234087</t>
-  </si>
-  <si>
-    <t>1995-07-21</t>
-  </si>
-  <si>
-    <t>0821110003</t>
-  </si>
-  <si>
-    <t>900103</t>
+    <t>Pregnant, 2nd trimester</t>
   </si>
   <si>
     <t>MP-100004</t>
@@ -202,7 +265,28 @@
     <t>0821110004</t>
   </si>
   <si>
-    <t>900104</t>
+    <t>Hendrik van Wyk</t>
+  </si>
+  <si>
+    <t>0829001004</t>
+  </si>
+  <si>
+    <t>Son</t>
+  </si>
+  <si>
+    <t>AB+</t>
+  </si>
+  <si>
+    <t>Arthritis;High cholesterol</t>
+  </si>
+  <si>
+    <t>Atorvastatin;Celebrex</t>
+  </si>
+  <si>
+    <t>Dr S Pillay</t>
+  </si>
+  <si>
+    <t>Self-funded patient</t>
   </si>
   <si>
     <t>MP-100005</t>
@@ -226,7 +310,40 @@
     <t>0821110005</t>
   </si>
   <si>
-    <t>900105</t>
+    <t>GEMS</t>
+  </si>
+  <si>
+    <t>Sapphire</t>
+  </si>
+  <si>
+    <t>GM2200987</t>
+  </si>
+  <si>
+    <t>Thabo Khumalo</t>
+  </si>
+  <si>
+    <t>0829001005</t>
+  </si>
+  <si>
+    <t>Father</t>
+  </si>
+  <si>
+    <t>O-</t>
+  </si>
+  <si>
+    <t>Aspirin;Shellfish</t>
+  </si>
+  <si>
+    <t>Epilepsy</t>
+  </si>
+  <si>
+    <t>Epilim</t>
+  </si>
+  <si>
+    <t>Dr L Mahlangu</t>
+  </si>
+  <si>
+    <t>Student, evening slots only</t>
   </si>
 </sst>
 </file>
@@ -727,255 +844,255 @@
         <v>38</v>
       </c>
       <c r="T2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I3" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="J3" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="K3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L3" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="M3" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="N3" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="O3" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="P3" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="Q3" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="R3" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="S3" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="T3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="E4" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="G4" t="s">
         <v>26</v>
       </c>
       <c r="H4" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="I4" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="J4" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="K4" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="L4" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="M4" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="N4" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="O4" t="s">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="P4" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="Q4" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="R4" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="S4" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="T4" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="F5" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="G5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H5" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="I5" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="J5" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="K5" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="L5" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="M5" t="s">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="N5" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="O5" t="s">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="P5" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="Q5" t="s">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="R5" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="S5" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="T5" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="F6" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="G6" t="s">
         <v>26</v>
       </c>
       <c r="H6" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="I6" t="s">
-        <v>28</v>
+        <v>99</v>
       </c>
       <c r="J6" t="s">
-        <v>29</v>
+        <v>100</v>
       </c>
       <c r="K6" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="L6" t="s">
-        <v>31</v>
+        <v>102</v>
       </c>
       <c r="M6" t="s">
-        <v>32</v>
+        <v>103</v>
       </c>
       <c r="N6" t="s">
-        <v>33</v>
+        <v>104</v>
       </c>
       <c r="O6" t="s">
-        <v>34</v>
+        <v>105</v>
       </c>
       <c r="P6" t="s">
-        <v>35</v>
+        <v>106</v>
       </c>
       <c r="Q6" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="R6" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="S6" t="s">
-        <v>38</v>
+        <v>109</v>
       </c>
       <c r="T6" t="s">
-        <v>38</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/project/sample-imports/patients-sample.xlsx
+++ b/project/sample-imports/patients-sample.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="72">
   <si>
     <t>file_number</t>
   </si>
@@ -73,7 +73,7 @@
     <t>notes</t>
   </si>
   <si>
-    <t>MP-100001</t>
+    <t>UAT-P-001</t>
   </si>
   <si>
     <t>Thandi</t>
@@ -82,7 +82,7 @@
     <t>Nkosi</t>
   </si>
   <si>
-    <t>makabmahlalela@gmail.com</t>
+    <t>makabmahlalela+patient1@gmail.com</t>
   </si>
   <si>
     <t>8803141234087</t>
@@ -94,7 +94,7 @@
     <t>female</t>
   </si>
   <si>
-    <t>0821110001</t>
+    <t>0825550001</t>
   </si>
   <si>
     <t>Discovery Health</t>
@@ -103,22 +103,22 @@
     <t>Classic Saver</t>
   </si>
   <si>
-    <t>900100123</t>
-  </si>
-  <si>
-    <t>Sibusiso Nkosi</t>
-  </si>
-  <si>
-    <t>0829001001</t>
-  </si>
-  <si>
-    <t>Husband</t>
+    <t>900101</t>
+  </si>
+  <si>
+    <t>Test Contact</t>
+  </si>
+  <si>
+    <t>0829990000</t>
+  </si>
+  <si>
+    <t>Sibling</t>
   </si>
   <si>
     <t>O+</t>
   </si>
   <si>
-    <t>Penicillin;Latex</t>
+    <t>Penicillin</t>
   </si>
   <si>
     <t>Asthma</t>
@@ -127,13 +127,10 @@
     <t>Ventolin</t>
   </si>
   <si>
-    <t>Dr A Naidoo</t>
-  </si>
-  <si>
-    <t>Prefers morning appointments</t>
-  </si>
-  <si>
-    <t>MP-100002</t>
+    <t/>
+  </si>
+  <si>
+    <t>UAT-P-002</t>
   </si>
   <si>
     <t>Sipho</t>
@@ -142,7 +139,7 @@
     <t>Dube</t>
   </si>
   <si>
-    <t>sipho.dube.test@example.com</t>
+    <t>maziyamayo7+patient2@gmail.com</t>
   </si>
   <si>
     <t>7911025234080</t>
@@ -154,46 +151,13 @@
     <t>male</t>
   </si>
   <si>
-    <t>0821110002</t>
-  </si>
-  <si>
-    <t>Bonitas</t>
-  </si>
-  <si>
-    <t>BonComprehensive</t>
-  </si>
-  <si>
-    <t>BN4455210</t>
-  </si>
-  <si>
-    <t>Nomvula Dube</t>
-  </si>
-  <si>
-    <t>0829001002</t>
-  </si>
-  <si>
-    <t>Wife</t>
-  </si>
-  <si>
-    <t>A+</t>
-  </si>
-  <si>
-    <t>Sulfa drugs</t>
-  </si>
-  <si>
-    <t>Hypertension;Type 2 diabetes</t>
-  </si>
-  <si>
-    <t>Amlodipine;Metformin</t>
-  </si>
-  <si>
-    <t>Dr P Govender</t>
-  </si>
-  <si>
-    <t>Diabetic review every 3 months</t>
-  </si>
-  <si>
-    <t>MP-100003</t>
+    <t>0825550002</t>
+  </si>
+  <si>
+    <t>900102</t>
+  </si>
+  <si>
+    <t>UAT-P-003</t>
   </si>
   <si>
     <t>Lerato</t>
@@ -202,7 +166,7 @@
     <t>Molefe</t>
   </si>
   <si>
-    <t>lerato.molefe.test@example.com</t>
+    <t>makabmahlalela+patient3@gmail.com</t>
   </si>
   <si>
     <t>9507212234087</t>
@@ -211,40 +175,13 @@
     <t>1995-07-21</t>
   </si>
   <si>
-    <t>0821110003</t>
-  </si>
-  <si>
-    <t>Momentum Health</t>
-  </si>
-  <si>
-    <t>Ingwe</t>
-  </si>
-  <si>
-    <t>MM7788341</t>
-  </si>
-  <si>
-    <t>Palesa Molefe</t>
-  </si>
-  <si>
-    <t>0829001003</t>
-  </si>
-  <si>
-    <t>Mother</t>
-  </si>
-  <si>
-    <t>B-</t>
-  </si>
-  <si>
-    <t>Peanuts</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Pregnant, 2nd trimester</t>
-  </si>
-  <si>
-    <t>MP-100004</t>
+    <t>0825550003</t>
+  </si>
+  <si>
+    <t>900103</t>
+  </si>
+  <si>
+    <t>UAT-P-004</t>
   </si>
   <si>
     <t>Pieter</t>
@@ -253,7 +190,7 @@
     <t>van Wyk</t>
   </si>
   <si>
-    <t>pieter.vanwyk.test@example.com</t>
+    <t>maziyamayo7+patient4@gmail.com</t>
   </si>
   <si>
     <t>6801306234084</t>
@@ -262,34 +199,13 @@
     <t>1968-01-30</t>
   </si>
   <si>
-    <t>0821110004</t>
-  </si>
-  <si>
-    <t>Hendrik van Wyk</t>
-  </si>
-  <si>
-    <t>0829001004</t>
-  </si>
-  <si>
-    <t>Son</t>
-  </si>
-  <si>
-    <t>AB+</t>
-  </si>
-  <si>
-    <t>Arthritis;High cholesterol</t>
-  </si>
-  <si>
-    <t>Atorvastatin;Celebrex</t>
-  </si>
-  <si>
-    <t>Dr S Pillay</t>
-  </si>
-  <si>
-    <t>Self-funded patient</t>
-  </si>
-  <si>
-    <t>MP-100005</t>
+    <t>0825550004</t>
+  </si>
+  <si>
+    <t>900104</t>
+  </si>
+  <si>
+    <t>UAT-P-005</t>
   </si>
   <si>
     <t>Naledi</t>
@@ -298,7 +214,7 @@
     <t>Khumalo</t>
   </si>
   <si>
-    <t>naledi.khumalo.test@example.com</t>
+    <t>makabmahlalela+patient5@gmail.com</t>
   </si>
   <si>
     <t>0109093234085</t>
@@ -307,43 +223,10 @@
     <t>2001-09-09</t>
   </si>
   <si>
-    <t>0821110005</t>
-  </si>
-  <si>
-    <t>GEMS</t>
-  </si>
-  <si>
-    <t>Sapphire</t>
-  </si>
-  <si>
-    <t>GM2200987</t>
-  </si>
-  <si>
-    <t>Thabo Khumalo</t>
-  </si>
-  <si>
-    <t>0829001005</t>
-  </si>
-  <si>
-    <t>Father</t>
-  </si>
-  <si>
-    <t>O-</t>
-  </si>
-  <si>
-    <t>Aspirin;Shellfish</t>
-  </si>
-  <si>
-    <t>Epilepsy</t>
-  </si>
-  <si>
-    <t>Epilim</t>
-  </si>
-  <si>
-    <t>Dr L Mahlangu</t>
-  </si>
-  <si>
-    <t>Student, evening slots only</t>
+    <t>0825550005</t>
+  </si>
+  <si>
+    <t>900105</t>
   </si>
 </sst>
 </file>
@@ -844,255 +727,255 @@
         <v>38</v>
       </c>
       <c r="T2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" t="s">
         <v>40</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>41</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>42</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>43</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>44</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>45</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>46</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" t="s">
         <v>47</v>
       </c>
-      <c r="I3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K3" t="s">
-        <v>50</v>
-      </c>
       <c r="L3" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="M3" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="N3" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="O3" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="P3" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="Q3" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="R3" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="S3" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="T3" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="E4" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="G4" t="s">
         <v>26</v>
       </c>
       <c r="H4" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="I4" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="J4" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="K4" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="L4" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="M4" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="N4" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="O4" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="P4" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="Q4" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="R4" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="S4" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="T4" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="F5" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="G5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H5" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="I5" t="s">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="J5" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="K5" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="L5" t="s">
-        <v>84</v>
+        <v>31</v>
       </c>
       <c r="M5" t="s">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="N5" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="O5" t="s">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="P5" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="Q5" t="s">
-        <v>88</v>
+        <v>36</v>
       </c>
       <c r="R5" t="s">
-        <v>89</v>
+        <v>37</v>
       </c>
       <c r="S5" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="T5" t="s">
-        <v>91</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="E6" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="F6" t="s">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="G6" t="s">
         <v>26</v>
       </c>
       <c r="H6" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="I6" t="s">
-        <v>99</v>
+        <v>28</v>
       </c>
       <c r="J6" t="s">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="K6" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="L6" t="s">
-        <v>102</v>
+        <v>31</v>
       </c>
       <c r="M6" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="N6" t="s">
-        <v>104</v>
+        <v>33</v>
       </c>
       <c r="O6" t="s">
-        <v>105</v>
+        <v>34</v>
       </c>
       <c r="P6" t="s">
-        <v>106</v>
+        <v>35</v>
       </c>
       <c r="Q6" t="s">
-        <v>107</v>
+        <v>36</v>
       </c>
       <c r="R6" t="s">
-        <v>108</v>
+        <v>37</v>
       </c>
       <c r="S6" t="s">
-        <v>109</v>
+        <v>38</v>
       </c>
       <c r="T6" t="s">
-        <v>110</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
